--- a/artfynd/A 9599-2025 artfynd.xlsx
+++ b/artfynd/A 9599-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73928246</v>
+        <v>111969701</v>
       </c>
       <c r="B2" t="n">
-        <v>87558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3483</v>
+        <v>472</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rutbläcksvamp</t>
+          <t>Silkesspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coprinopsis picacea</t>
+          <t>Cortinarius turgidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vångaberget, Sk</t>
+          <t>Kädarpsvägen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461013.0999851502</v>
+        <v>461069</v>
       </c>
       <c r="R2" t="n">
-        <v>6221896.956943734</v>
+        <v>6221571</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,73 +757,78 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bokskog</t>
+          <t>bokskog, vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Tony Svensson, Lennart Söderberg, Bengt Hertzman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73928241</v>
+        <v>80379507</v>
       </c>
       <c r="B3" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>474</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rävspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius vulpinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Velen.) Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vångaberget, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461019.8853607936</v>
+        <v>461093</v>
       </c>
       <c r="R3" t="n">
-        <v>6222152.03627751</v>
+        <v>6221569</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>7 fruktkroppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +879,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Bokskog</t>
+          <t>Äldre bokskog, vägkant vid grusväg</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Under bok</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Under bok</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73928243</v>
+        <v>73928242</v>
       </c>
       <c r="B4" t="n">
-        <v>75910</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1342</v>
+        <v>924</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461019.8853607936</v>
+        <v>461020</v>
       </c>
       <c r="R4" t="n">
-        <v>6222152.03627751</v>
+        <v>6222152</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +975,9 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73928242</v>
+        <v>73928243</v>
       </c>
       <c r="B5" t="n">
-        <v>77323</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>924</v>
+        <v>1342</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461019.8853607936</v>
+        <v>461020</v>
       </c>
       <c r="R5" t="n">
-        <v>6222152.03627751</v>
+        <v>6222152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1077,9 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,56 +1111,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111969701</v>
+        <v>73928244</v>
       </c>
       <c r="B6" t="n">
-        <v>85679</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>472</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Silkesspindling</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius turgidus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kädarpsvägen, Sk</t>
+          <t>Vångaberget, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461069</v>
+        <v>461042</v>
       </c>
       <c r="R6" t="n">
-        <v>6221570</v>
+        <v>6222137</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,12 +1176,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,85 +1190,73 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>bokskog, vägkant</t>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bokhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tony Svensson, Lennart Söderberg, Bengt Hertzman</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111970733</v>
+        <v>73928241</v>
       </c>
       <c r="B7" t="n">
-        <v>85304</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>235079</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lövfagerspindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius calochrous</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Gray</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kädarpsvägen, Sk</t>
+          <t>Vångaberget, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461088</v>
+        <v>461020</v>
       </c>
       <c r="R7" t="n">
-        <v>6221578</v>
+        <v>6222152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,12 +1283,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,27 +1297,562 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Bokskog, vägkant</t>
+          <t>Bokskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>73928246</v>
+      </c>
+      <c r="B8" t="n">
+        <v>88540</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3483</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rutbläcksvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Coprinopsis picacea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vångaberget, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>461013</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6221897</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kiaby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>73928240</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vångaberget, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>461035</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6222170</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>73928245</v>
+      </c>
+      <c r="B10" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vångaberget, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>461042</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6222137</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kiaby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bokhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111970733</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87219</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>235079</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lövfagerspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius callochrous</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kädarpsvägen, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>461088</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6221578</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kiaby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Bokskog, vägkant</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Tony Svensson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Tony Svensson, Nils Otto Nilsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111969627</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91437</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>256842</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sydlig taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramaria spinulosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kädarpsvägen, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>461143</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6221638</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kiaby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ska kollas.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>bokskog, vägkant</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tony Svensson, Lennart Söderberg, Bengt Hertzman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9599-2025 artfynd.xlsx
+++ b/artfynd/A 9599-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111969701</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80379507</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928242</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928243</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928244</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928241</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928246</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1521,6 +1561,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928240</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1628,6 +1673,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73928245</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111970733</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,8 +1908,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111969627</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 9599-2025 artfynd.xlsx
+++ b/artfynd/A 9599-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1681,56 +1681,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111970733</v>
+        <v>136134099</v>
       </c>
       <c r="B11" t="n">
-        <v>87219</v>
+        <v>56911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>235079</v>
+        <v>208255</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lövfagerspindling</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius callochrous</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kädarpsvägen, Sk</t>
+          <t>Munkahålen, Munkahålen, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461088</v>
+        <v>460876</v>
       </c>
       <c r="R11" t="n">
-        <v>6221578</v>
+        <v>6222041</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,12 +1746,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,65 +1760,67 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Bokskog, vägkant</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tony Svensson, Nils Otto Nilsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111970733</t>
+          <t>https://artportalen.se/Sighting/136134099</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111969627</v>
+        <v>111970733</v>
       </c>
       <c r="B12" t="n">
-        <v>91437</v>
+        <v>87219</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>256842</v>
+        <v>235079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sydlig taggfingersvamp</t>
+          <t>Lövfagerspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria spinulosa</t>
+          <t>Cortinarius callochrous</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1838,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461143</v>
+        <v>461088</v>
       </c>
       <c r="R12" t="n">
-        <v>6221638</v>
+        <v>6221578</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,24 +1859,19 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ska kollas.</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
@@ -1893,7 +1879,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>bokskog, vägkant</t>
+          <t>Bokskog, vägkant</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1904,11 +1890,127 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tony Svensson, Lennart Söderberg, Bengt Hertzman</t>
+          <t>Tony Svensson, Nils Otto Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111970733</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>111969627</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91437</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>256842</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sydlig taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramaria spinulosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kädarpsvägen, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>461143</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6221638</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kiaby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ska kollas.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>bokskog, vägkant</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tony Svensson, Lennart Söderberg, Bengt Hertzman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111969627</t>
         </is>
@@ -1927,6 +2029,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9599-2025 artfynd.xlsx
+++ b/artfynd/A 9599-2025 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>136134099</v>
       </c>
       <c r="B11" t="n">
-        <v>56911</v>
+        <v>56912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9599-2025 artfynd.xlsx
+++ b/artfynd/A 9599-2025 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>136134099</v>
       </c>
       <c r="B11" t="n">
-        <v>56912</v>
+        <v>56916</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9599-2025 artfynd.xlsx
+++ b/artfynd/A 9599-2025 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>136134099</v>
       </c>
       <c r="B11" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9599-2025 artfynd.xlsx
+++ b/artfynd/A 9599-2025 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>136134099</v>
       </c>
       <c r="B11" t="n">
-        <v>56917</v>
+        <v>56922</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9599-2025 artfynd.xlsx
+++ b/artfynd/A 9599-2025 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>136134099</v>
       </c>
       <c r="B11" t="n">
-        <v>56922</v>
+        <v>56935</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
